--- a/output/Data and Chart Outputs/kosovo_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/kosovo_power_generation_daily.xlsx
@@ -155,7 +155,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Kosovo power generation by type (ENTSO-E) (to Aug/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Kosovo power generation by type (ENTSO-E) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -888,7 +889,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-03 09:54 UTC; 1861 days, 2021-08-23 to 2026-09-28</t>
+          <t>2026-10-28 00:44 UTC; 1888 days, 2021-08-23 to 2026-10-25</t>
         </is>
       </c>
     </row>
@@ -953,22 +954,22 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2131</v>
+        <v>0.3013</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6533</v>
+        <v>4.1115</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>152.6793</v>
+        <v>408.3694</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -979,22 +980,22 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3013</v>
+        <v>0.7644999999999998</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1115</v>
+        <v>4.411700000000001</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>408.3694</v>
+        <v>527.8292999999999</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1005,22 +1006,22 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7645</v>
+        <v>0.393</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4117</v>
+        <v>4.382</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>527.8293000000001</v>
+        <v>555.874</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1031,22 +1032,22 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B5" t="n">
-        <v>0.393</v>
+        <v>0.7451</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>4.382</v>
+        <v>8.2097</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>555.874</v>
+        <v>469.1074</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1057,22 +1058,22 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7451</v>
+        <v>0.8802</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>8.209700000000002</v>
+        <v>9.257100000000001</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>469.1074</v>
+        <v>479.9719</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1083,22 +1084,22 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8802</v>
+        <v>0.6217</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>9.257100000000001</v>
+        <v>8.507899999999999</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>479.9719</v>
+        <v>500.7711</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1109,22 +1110,22 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6217</v>
+        <v>0.7795000000000002</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>8.507899999999999</v>
+        <v>7.698099999999998</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>500.7711</v>
+        <v>610.6442000000001</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1135,22 +1136,22 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7795</v>
+        <v>3.9682</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>7.6981</v>
+        <v>8.994999999999997</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>610.6442</v>
+        <v>515.5690000000001</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1161,22 +1162,22 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B10" t="n">
-        <v>3.9682</v>
+        <v>5.264500000000001</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>8.994999999999999</v>
+        <v>4.2178</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>515.569</v>
+        <v>481.1287</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1187,22 +1188,22 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B11" t="n">
-        <v>5.2645</v>
+        <v>3.0397</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>4.2178</v>
+        <v>12.2498</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>481.1287</v>
+        <v>507.4939</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1213,22 +1214,22 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B12" t="n">
-        <v>3.0397</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>12.2498</v>
+        <v>23.026</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>507.4939</v>
+        <v>427.4866999999999</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1239,7 +1240,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
@@ -1248,13 +1249,13 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>23.026</v>
+        <v>20.1144</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>427.4867</v>
+        <v>408.3812</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1265,7 +1266,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -1274,13 +1275,13 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>20.1144</v>
+        <v>34.9264</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>408.3812</v>
+        <v>419.0098</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1291,7 +1292,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
@@ -1300,13 +1301,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34.9264</v>
+        <v>23.8713</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>419.0098</v>
+        <v>425.2856999999999</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1317,22 +1318,22 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2.6645</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23.8713</v>
+        <v>38.1804</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>425.2857</v>
+        <v>486.0114</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1343,22 +1344,22 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B17" t="n">
-        <v>2.6645</v>
+        <v>11.355</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>38.1804</v>
+        <v>37.12749999999999</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>486.0114</v>
+        <v>535.4354</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1369,22 +1370,22 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B18" t="n">
-        <v>11.355</v>
+        <v>4.191500000000001</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>37.1275</v>
+        <v>33.26329999999999</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>535.4354000000001</v>
+        <v>509.2134</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1395,22 +1396,22 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>44927</v>
+        <v>44958</v>
       </c>
       <c r="B19" t="n">
-        <v>4.1915</v>
+        <v>1.3282</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>33.2633</v>
+        <v>41.8054</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>509.2134</v>
+        <v>447.3795999999999</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1421,22 +1422,22 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B20" t="n">
-        <v>1.3282</v>
+        <v>2.1102</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>41.8054</v>
+        <v>29.9285</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>447.3796</v>
+        <v>498.035</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1447,22 +1448,22 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B21" t="n">
-        <v>2.1102</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>29.9285</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>498.035</v>
+        <v>406.7755</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1473,7 +1474,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B22" t="n">
         <v>0</v>
@@ -1488,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>406.7755</v>
+        <v>372.6491</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1499,7 +1500,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B23" t="n">
         <v>0</v>
@@ -1514,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>372.6491</v>
+        <v>352.2399</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1525,7 +1526,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B24" t="n">
         <v>0</v>
@@ -1540,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>352.2399</v>
+        <v>394.5099</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1551,7 +1552,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
@@ -1566,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>394.5099</v>
+        <v>351.8773</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1577,7 +1578,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -1592,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>351.8773</v>
+        <v>344.7114999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1603,7 +1604,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -1618,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>344.7115</v>
+        <v>385.5825999999999</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1629,7 +1630,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -1644,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>385.5826</v>
+        <v>477.3001</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1655,7 +1656,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -1670,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>477.3001</v>
+        <v>532.3575999999999</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1681,7 +1682,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -1696,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>532.3575999999999</v>
+        <v>516.6189000000001</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1707,7 +1708,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -1722,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>516.6189000000001</v>
+        <v>517.0137999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1733,7 +1734,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -1748,7 +1749,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>517.0137999999999</v>
+        <v>513.9194</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1759,7 +1760,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B33" t="n">
         <v>0</v>
@@ -1774,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>513.9194</v>
+        <v>485.2072999999999</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1785,7 +1786,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -1800,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>485.2073</v>
+        <v>526.5608999999999</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1811,7 +1812,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B35" t="n">
         <v>0</v>
@@ -1826,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>526.5609000000001</v>
+        <v>496.9213</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1837,7 +1838,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B36" t="n">
         <v>0</v>
@@ -1852,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>496.9213</v>
+        <v>391.0445</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1863,7 +1864,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B37" t="n">
         <v>0</v>
@@ -1878,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>391.0445</v>
+        <v>410.2449</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1889,7 +1890,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B38" t="n">
         <v>0</v>
@@ -1904,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>410.2449</v>
+        <v>333.3025</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1915,7 +1916,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B39" t="n">
         <v>0</v>
@@ -1930,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>333.3025</v>
+        <v>463.4985</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1941,7 +1942,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B40" t="n">
         <v>0</v>
@@ -1956,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>463.4985</v>
+        <v>500.8678</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1967,7 +1968,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>45597</v>
+        <v>45627</v>
       </c>
       <c r="B41" t="n">
         <v>0</v>
@@ -1982,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>500.8678</v>
+        <v>473.7021</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1993,7 +1994,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="B42" t="n">
         <v>0</v>
@@ -2008,7 +2009,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>473.7021</v>
+        <v>523.3513</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -2019,7 +2020,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B43" t="n">
         <v>0</v>
@@ -2034,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>523.3513</v>
+        <v>456.0197999999999</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -2045,7 +2046,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B44" t="n">
         <v>0</v>
@@ -2060,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>456.0198</v>
+        <v>464.4093999999999</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2071,7 +2072,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B45" t="n">
         <v>0</v>
@@ -2086,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>464.4093999999999</v>
+        <v>290.9679</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2097,7 +2098,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B46" t="n">
         <v>0</v>
@@ -2112,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>290.9679</v>
+        <v>298.7579</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2123,7 +2124,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
@@ -2138,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>298.7579</v>
+        <v>288.8503000000001</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2149,7 +2150,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
@@ -2164,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>288.8503</v>
+        <v>352.786</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2175,7 +2176,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
@@ -2190,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>352.786</v>
+        <v>325.9524999999999</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2201,7 +2202,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
@@ -2216,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>325.9525</v>
+        <v>346.2983</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2227,7 +2228,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
@@ -2242,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>346.2983</v>
+        <v>468.2114999999999</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2253,7 +2254,7 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B52" t="n">
         <v>0</v>
@@ -2268,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>468.2115</v>
+        <v>478.8849</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2279,7 +2280,7 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B53" t="n">
         <v>0</v>
@@ -2294,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>478.8849</v>
+        <v>547.9400000000001</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2305,7 +2306,7 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B54" t="n">
         <v>0</v>
@@ -2320,7 +2321,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>547.9400000000001</v>
+        <v>563.9400000000001</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2331,7 +2332,7 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B55" t="n">
         <v>0</v>
@@ -2346,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>563.9400000000001</v>
+        <v>497.8629999999999</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2357,7 +2358,7 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B56" t="n">
         <v>0</v>
@@ -2372,7 +2373,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>497.863</v>
+        <v>490.7161</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2383,7 +2384,7 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B57" t="n">
         <v>0</v>
@@ -2398,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>490.7161</v>
+        <v>332.1238</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2409,7 +2410,7 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B58" t="n">
         <v>0</v>
@@ -2424,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>332.1238</v>
+        <v>162.7726</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2435,7 +2436,7 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B59" t="n">
         <v>0</v>
@@ -2450,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>162.7726</v>
+        <v>338.2133000000001</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2461,7 +2462,7 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B60" t="n">
         <v>0</v>
@@ -2476,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>338.2133</v>
+        <v>390.2217</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2487,7 +2488,7 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B61" t="n">
         <v>0</v>
@@ -2502,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>390.2217</v>
+        <v>383.8979</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2513,7 +2514,7 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B62" t="n">
         <v>0</v>
@@ -2528,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>383.8979</v>
+        <v>354.6265</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2549,7 +2550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1862"/>
+  <dimension ref="A1:P1889"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95684,6 +95685,1356 @@
         <v>14760.2</v>
       </c>
     </row>
+    <row r="1863">
+      <c r="A1863" s="4" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1863" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1863" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1863" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1863" t="n">
+        <v>15178.3</v>
+      </c>
+      <c r="F1863" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1863" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1863" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1863" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1863" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1863" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1863" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1863" t="n">
+        <v>15178.3</v>
+      </c>
+      <c r="N1863" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1863" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1863" t="n">
+        <v>14635.5</v>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1864" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1864" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1864" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1864" t="n">
+        <v>15376.8</v>
+      </c>
+      <c r="F1864" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1864" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1864" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1864" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1864" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1864" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1864" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1864" t="n">
+        <v>15376.8</v>
+      </c>
+      <c r="N1864" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1864" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1864" t="n">
+        <v>14487.8</v>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1865" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1865" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1865" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1865" t="n">
+        <v>15414.5</v>
+      </c>
+      <c r="F1865" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1865" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1865" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1865" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1865" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1865" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1865" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1865" t="n">
+        <v>15414.5</v>
+      </c>
+      <c r="N1865" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1865" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1865" t="n">
+        <v>14796.7</v>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1866" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1866" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1866" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1866" t="n">
+        <v>15468.6</v>
+      </c>
+      <c r="F1866" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1866" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1866" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1866" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1866" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1866" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1866" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1866" t="n">
+        <v>15468.6</v>
+      </c>
+      <c r="N1866" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1866" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1866" t="n">
+        <v>14828.2</v>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B1867" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1867" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1867" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1867" t="n">
+        <v>15270.8</v>
+      </c>
+      <c r="F1867" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1867" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1867" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1867" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1867" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1867" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1867" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1867" t="n">
+        <v>15270.8</v>
+      </c>
+      <c r="N1867" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1867" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1867" t="n">
+        <v>14721.2</v>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B1868" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1868" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1868" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1868" t="n">
+        <v>15027.3</v>
+      </c>
+      <c r="F1868" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1868" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1868" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1868" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1868" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1868" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1868" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1868" t="n">
+        <v>15027.3</v>
+      </c>
+      <c r="N1868" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1868" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1868" t="n">
+        <v>14476.3</v>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1869" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1869" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1869" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1869" t="n">
+        <v>12236.7</v>
+      </c>
+      <c r="F1869" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1869" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1869" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1869" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1869" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1869" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1869" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1869" t="n">
+        <v>12236.7</v>
+      </c>
+      <c r="N1869" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1869" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1869" t="n">
+        <v>15334</v>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1870" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1870" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1870" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1870" t="n">
+        <v>12370.5</v>
+      </c>
+      <c r="F1870" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1870" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1870" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1870" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1870" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1870" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1870" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1870" t="n">
+        <v>12370.5</v>
+      </c>
+      <c r="N1870" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1870" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1870" t="n">
+        <v>15367</v>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1871" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1871" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1871" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1871" t="n">
+        <v>12326.4</v>
+      </c>
+      <c r="F1871" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1871" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1871" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1871" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1871" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1871" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1871" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1871" t="n">
+        <v>12326.4</v>
+      </c>
+      <c r="N1871" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1871" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1871" t="n">
+        <v>15433.3</v>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1872" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1872" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1872" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1872" t="n">
+        <v>4638.1</v>
+      </c>
+      <c r="F1872" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1872" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1872" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1872" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1872" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1872" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1872" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1872" t="n">
+        <v>4638.1</v>
+      </c>
+      <c r="N1872" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1872" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1872" t="n">
+        <v>15662.2</v>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1873" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1873" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1873" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1873" t="n">
+        <v>10773.8</v>
+      </c>
+      <c r="F1873" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1873" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1873" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1873" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1873" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1873" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1873" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1873" t="n">
+        <v>10773.8</v>
+      </c>
+      <c r="N1873" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1873" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1873" t="n">
+        <v>15372.6</v>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1874" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1874" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1874" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1874" t="n">
+        <v>9422.1</v>
+      </c>
+      <c r="F1874" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1874" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1874" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1874" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1874" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1874" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1874" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1874" t="n">
+        <v>9422.1</v>
+      </c>
+      <c r="N1874" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1874" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1874" t="n">
+        <v>14150.4</v>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B1875" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1875" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1875" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1875" t="n">
+        <v>9512.799999999999</v>
+      </c>
+      <c r="F1875" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1875" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1875" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1875" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1875" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1875" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1875" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1875" t="n">
+        <v>9512.799999999999</v>
+      </c>
+      <c r="N1875" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1875" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1875" t="n">
+        <v>14327.4</v>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1876" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1876" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1876" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1876" t="n">
+        <v>11066.3</v>
+      </c>
+      <c r="F1876" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1876" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1876" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1876" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1876" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1876" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1876" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1876" t="n">
+        <v>11066.3</v>
+      </c>
+      <c r="N1876" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1876" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1876" t="n">
+        <v>15156.6</v>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1877" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1877" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1877" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1877" t="n">
+        <v>12619.7</v>
+      </c>
+      <c r="F1877" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1877" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1877" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1877" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1877" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1877" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1877" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1877" t="n">
+        <v>12619.7</v>
+      </c>
+      <c r="N1877" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1877" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1877" t="n">
+        <v>17146</v>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1878" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1878" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1878" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1878" t="n">
+        <v>12707.8</v>
+      </c>
+      <c r="F1878" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1878" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1878" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1878" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1878" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1878" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1878" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1878" t="n">
+        <v>12707.8</v>
+      </c>
+      <c r="N1878" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1878" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1878" t="n">
+        <v>17349</v>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1879" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1879" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1879" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1879" t="n">
+        <v>12434.7</v>
+      </c>
+      <c r="F1879" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1879" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1879" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1879" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1879" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1879" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1879" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1879" t="n">
+        <v>12434.7</v>
+      </c>
+      <c r="N1879" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1879" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1879" t="n">
+        <v>17819.9</v>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1880" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1880" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1880" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1880" t="n">
+        <v>12418.5</v>
+      </c>
+      <c r="F1880" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1880" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1880" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1880" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1880" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1880" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1880" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1880" t="n">
+        <v>12418.5</v>
+      </c>
+      <c r="N1880" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1880" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1880" t="n">
+        <v>18289.2</v>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B1881" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1881" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1881" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1881" t="n">
+        <v>12273.6</v>
+      </c>
+      <c r="F1881" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1881" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1881" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1881" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1881" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1881" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1881" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1881" t="n">
+        <v>12273.6</v>
+      </c>
+      <c r="N1881" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1881" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1881" t="n">
+        <v>18269.4</v>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B1882" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1882" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1882" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1882" t="n">
+        <v>14225</v>
+      </c>
+      <c r="F1882" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1882" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1882" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1882" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1882" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1882" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1882" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1882" t="n">
+        <v>14225</v>
+      </c>
+      <c r="N1882" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1882" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1882" t="n">
+        <v>17353.2</v>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1883" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1883" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1883" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1883" t="n">
+        <v>15393.5</v>
+      </c>
+      <c r="F1883" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1883" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1883" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1883" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1883" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1883" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1883" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1883" t="n">
+        <v>15393.5</v>
+      </c>
+      <c r="N1883" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1883" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1883" t="n">
+        <v>17000.4</v>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1884" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1884" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1884" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1884" t="n">
+        <v>15346.5</v>
+      </c>
+      <c r="F1884" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1884" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1884" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1884" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1884" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1884" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1884" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1884" t="n">
+        <v>15346.5</v>
+      </c>
+      <c r="N1884" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1884" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1884" t="n">
+        <v>16694.6</v>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1885" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1885" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1885" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1885" t="n">
+        <v>15155.8</v>
+      </c>
+      <c r="F1885" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1885" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1885" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1885" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1885" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1885" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1885" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1885" t="n">
+        <v>15155.8</v>
+      </c>
+      <c r="N1885" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1885" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1885" t="n">
+        <v>17120.1</v>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1886" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1886" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1886" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1886" t="n">
+        <v>14865.2</v>
+      </c>
+      <c r="F1886" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1886" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1886" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1886" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1886" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1886" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1886" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1886" t="n">
+        <v>14865.2</v>
+      </c>
+      <c r="N1886" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1886" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1886" t="n">
+        <v>16267.4</v>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1887" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1887" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1887" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1887" t="n">
+        <v>14840.2</v>
+      </c>
+      <c r="F1887" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1887" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1887" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1887" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1887" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1887" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1887" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1887" t="n">
+        <v>14840.2</v>
+      </c>
+      <c r="N1887" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1887" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1887" t="n">
+        <v>17226.2</v>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B1888" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1888" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1888" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1888" t="n">
+        <v>8955.9</v>
+      </c>
+      <c r="F1888" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1888" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1888" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1888" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1888" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1888" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1888" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1888" t="n">
+        <v>8955.9</v>
+      </c>
+      <c r="N1888" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1888" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1888" t="n">
+        <v>17054.7</v>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B1889" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1889" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1889" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1889" t="n">
+        <v>6044</v>
+      </c>
+      <c r="F1889" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1889" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1889" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1889" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1889" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1889" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1889" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1889" t="n">
+        <v>6044</v>
+      </c>
+      <c r="N1889" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1889" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1889" t="n">
+        <v>16345.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
